--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2941,52 +2941,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>76604189</v>
+        <v>135494581</v>
       </c>
       <c r="B21" t="n">
-        <v>103403</v>
+        <v>104419</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223246</v>
+        <v>222056</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Stor häxört</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Circaea lutetiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ringvägen, Sk</t>
+          <t>Stensoffaskogen, Sk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403071</v>
+        <v>402845</v>
       </c>
       <c r="R21" t="n">
-        <v>6173299</v>
+        <v>6173570</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3010,12 +3006,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3024,31 +3020,30 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Santeri Vanhanen</t>
+          <t>Stefan Bergström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Santeri Vanhanen</t>
+          <t>Stefan Bergström, Suvi Bergström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76604189</t>
+          <t>https://artportalen.se/Sighting/135494581</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>83468325</v>
+        <v>76604189</v>
       </c>
       <c r="B22" t="n">
         <v>103403</v>
@@ -3076,24 +3071,24 @@
           <t>Huds.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skogsalm (Skyddsvärt träd), Sk</t>
+          <t>Ringvägen, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402899</v>
+        <v>403071</v>
       </c>
       <c r="R22" t="n">
-        <v>6172817</v>
+        <v>6173299</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3115,19 +3110,14 @@
           <t>Silvåkra</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>282CDD0A-211B-4603-AF75-888559DAB267</t>
-        </is>
-      </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2009-04-21</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2009-04-21</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3136,34 +3126,31 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Per Levenskog</t>
+          <t>Santeri Vanhanen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Per Levenskog, Lotta Tornler</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Santeri Vanhanen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83468325</t>
+          <t>https://artportalen.se/Sighting/76604189</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127814995</v>
+        <v>83468325</v>
       </c>
       <c r="B23" t="n">
         <v>103403</v>
@@ -3191,20 +3178,24 @@
           <t>Huds.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>250 m O Stensoffan, Sk</t>
+          <t>Skogsalm (Skyddsvärt träd), Sk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>402720</v>
+        <v>402899</v>
       </c>
       <c r="R23" t="n">
-        <v>6172887</v>
+        <v>6172817</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3226,14 +3217,19 @@
           <t>Silvåkra</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>282CDD0A-211B-4603-AF75-888559DAB267</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2009-04-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2009-04-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3248,31 +3244,31 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Staffan Nilsson</t>
+          <t>Per Levenskog</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Staffan Nilsson</t>
+          <t>Per Levenskog, Lotta Tornler</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Floraövervakning Lund</t>
+          <t>Trädportalen</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127814995</t>
+          <t>https://artportalen.se/Sighting/83468325</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127815057</v>
+        <v>127814995</v>
       </c>
       <c r="B24" t="n">
-        <v>100459</v>
+        <v>103403</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3280,28 +3276,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>224698</v>
+        <v>223246</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lundäxing</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylis polygama</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Horv.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>250 m O Stensoffan, Sk</t>
@@ -3352,26 +3344,10 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>Biologiska Museet, Lunds Universitet</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>SNn 25-19</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>Torbjörn Tyler</t>
-        </is>
-      </c>
       <c r="AW24" t="inlineStr">
         <is>
           <t>Staffan Nilsson</t>
@@ -3389,54 +3365,58 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127815057</t>
+          <t>https://artportalen.se/Sighting/127814995</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>63798735</v>
+        <v>127815057</v>
       </c>
       <c r="B25" t="n">
-        <v>107718</v>
+        <v>100459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220015</v>
+        <v>224698</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Lundäxing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Campanula latifolia</t>
+          <t>Dactylis polygama</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Horv.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>200m OSO Silvåkragården, Sk</t>
+          <t>250 m O Stensoffan, Sk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>403773</v>
+        <v>402720</v>
       </c>
       <c r="R25" t="n">
-        <v>6172649</v>
+        <v>6172887</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3460,17 +3440,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1988-08-02</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1988-08-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Campanula latifolia/2D5a0931/Silvåkra s:n/HWl/ /Håkan Wittzell,Lund</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3479,64 +3454,70 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>lövskog, fåtalig</t>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>SkFlora     90555</t>
+          <t>SNn 25-19</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Staffan Nilsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Wittzell</t>
+          <t>Staffan Nilsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>Skånes Flora (1989-2006)</t>
+          <t>Floraövervakning Lund</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63798735</t>
+          <t>https://artportalen.se/Sighting/127815057</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>63798719</v>
+        <v>63798735</v>
       </c>
       <c r="B26" t="n">
-        <v>111018</v>
+        <v>107718</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222776</v>
+        <v>220015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Campanula latifolia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3581,17 +3562,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>1986-05-08</t>
+          <t>1988-08-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>1986-05-08</t>
+          <t>1988-08-02</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina/2D5a0931/Silvåkra s:n/HWl/ /Håkan Wittzell,Lund</t>
+          <t>Campanula latifolia/2D5a0931/Silvåkra s:n/HWl/ /Håkan Wittzell,Lund</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3605,12 +3586,12 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>lövskog</t>
+          <t>lövskog, fåtalig</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>SkFlora     90540</t>
+          <t>SkFlora     90555</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3631,38 +3612,38 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63798719</t>
+          <t>https://artportalen.se/Sighting/63798735</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>63798752</v>
+        <v>63798719</v>
       </c>
       <c r="B27" t="n">
-        <v>103402</v>
+        <v>111018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223246</v>
+        <v>222776</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3702,17 +3683,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>1988-08-02</t>
+          <t>1986-05-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>1988-08-02</t>
+          <t>1986-05-08</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ulmus glabra/2D5a0931/Silvåkra s:n/HWl/ /Håkan Wittzell,Lund</t>
+          <t>Adoxa moschatellina/2D5a0931/Silvåkra s:n/HWl/ /Håkan Wittzell,Lund</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3731,7 +3712,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>SkFlora     90569</t>
+          <t>SkFlora     90540</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3752,58 +3733,54 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63798752</t>
+          <t>https://artportalen.se/Sighting/63798719</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>65813057</v>
+        <v>63798752</v>
       </c>
       <c r="B28" t="n">
-        <v>58810</v>
+        <v>103402</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100118</v>
+        <v>223246</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelophylax esculentus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Krankesjön, Sk</t>
+          <t>200m OSO Silvåkragården, Sk</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404301</v>
+        <v>403773</v>
       </c>
       <c r="R28" t="n">
-        <v>6172716</v>
+        <v>6172649</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3827,22 +3804,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2017-05-21</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>1988-08-02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2017-05-21</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>1988-08-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ulmus glabra/2D5a0931/Silvåkra s:n/HWl/ /Håkan Wittzell,Lund</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3853,48 +3825,62 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>SkFlora     90569</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Klas Rådberg</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Klas Rådberg</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Håkan Wittzell</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/65813057</t>
+          <t>https://artportalen.se/Sighting/63798752</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113422848</v>
+        <v>65813057</v>
       </c>
       <c r="B29" t="n">
-        <v>58112</v>
+        <v>58810</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103020</v>
+        <v>100118</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Pelophylax esculentus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3904,30 +3890,22 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fodermatning ängen, Sk</t>
+          <t>Krankesjön, Sk</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404158</v>
+        <v>404301</v>
       </c>
       <c r="R29" t="n">
-        <v>6172779</v>
+        <v>6172716</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3951,22 +3929,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2017-05-21</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2017-05-21</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3981,74 +3959,77 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jonny Johansson</t>
+          <t>Klas Rådberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jonny Johansson</t>
+          <t>Klas Rådberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113422848</t>
+          <t>https://artportalen.se/Sighting/65813057</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>297988</v>
+        <v>113422848</v>
       </c>
       <c r="B30" t="n">
-        <v>105110</v>
+        <v>58112</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1084</v>
+        <v>103020</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neslia paniculata</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Desv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Silvåkragården, 1,0 km OSO, Sk</t>
+          <t>Fodermatning ängen, Sk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404623</v>
+        <v>404158</v>
       </c>
       <c r="R30" t="n">
-        <v>6172493</v>
+        <v>6172779</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4070,24 +4051,24 @@
           <t>Silvåkra</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>M-Lun-0186</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>1989-08-19</t>
+          <t>2023-11-27</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1989-08-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2D5a0739</t>
+          <t>2023-11-27</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4098,78 +4079,78 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>kornåker</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Skåne Floraväktarna</t>
+          <t>Jonny Johansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Wittzell</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/297988</t>
+          <t>https://artportalen.se/Sighting/113422848</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129471720</v>
+        <v>297988</v>
       </c>
       <c r="B31" t="n">
-        <v>88424</v>
+        <v>105110</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1008</v>
+        <v>1084</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Igelkottsröksvamp</t>
+          <t>Korndådra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycoperdon echinatum</t>
+          <t>Neslia paniculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Desv.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Almen, Almen, Sk</t>
+          <t>Silvåkragården, 1,0 km OSO, Sk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>403411</v>
+        <v>404623</v>
       </c>
       <c r="R31" t="n">
-        <v>6173143</v>
+        <v>6172493</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4191,24 +4172,24 @@
           <t>Silvåkra</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>M-Lun-0186</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>1989-08-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>1989-08-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2D5a0739</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4219,31 +4200,40 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>kornåker</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Andreas Emanuelsson</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Andreas Emanuelsson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Håkan Wittzell</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129471720</t>
+          <t>https://artportalen.se/Sighting/297988</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>453724</v>
+        <v>129471720</v>
       </c>
       <c r="B32" t="n">
-        <v>75390</v>
+        <v>88424</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4251,46 +4241,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1458</v>
+        <v>1008</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Solitärbok mellan Silvåkragården och Stensoffan, Sk</t>
+          <t>Almen, Almen, Sk</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>403432</v>
+        <v>403411</v>
       </c>
       <c r="R32" t="n">
-        <v>6172733</v>
+        <v>6173143</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4314,17 +4295,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2009-02-08</t>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2009-02-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På barken av död, grov bokhögstubbe.</t>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4339,65 +4325,74 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Andreas Malmqvist</t>
+          <t>Andreas Emanuelsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Andreas Malmqvist</t>
+          <t>Andreas Emanuelsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/453724</t>
+          <t>https://artportalen.se/Sighting/129471720</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>697114</v>
+        <v>453724</v>
       </c>
       <c r="B33" t="n">
-        <v>102843</v>
+        <v>75390</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1906</v>
+        <v>1458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revig blodrot</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Potentilla anglica</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Laichard.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Silvåkragården, 500 m NV, Sk</t>
+          <t>Solitärbok mellan Silvåkragården och Stensoffan, Sk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>403515</v>
+        <v>403432</v>
       </c>
       <c r="R33" t="n">
-        <v>6173296</v>
+        <v>6172733</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4419,24 +4414,19 @@
           <t>Silvåkra</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>M-Lun-0349</t>
-        </is>
-      </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1996-09-26</t>
+          <t>2009-02-08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1996-09-26</t>
+          <t>2009-02-08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>2D5a1528</t>
+          <t>På barken av död, grov bokhögstubbe.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4447,82 +4437,69 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>vägkant i odlad granskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Skåne Floraväktarna</t>
+          <t>Andreas Malmqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Skåne Floraväktarna</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/697114</t>
+          <t>https://artportalen.se/Sighting/453724</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3787</v>
+        <v>697114</v>
       </c>
       <c r="B34" t="n">
-        <v>58829</v>
+        <v>102843</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100141</v>
+        <v>1906</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Revig blodrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Potentilla anglica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Laichard.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Friesendorffs damm, Krankesjön, Sk</t>
+          <t>Silvåkragården, 500 m NV, Sk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>403472</v>
+        <v>403515</v>
       </c>
       <c r="R34" t="n">
-        <v>6172715</v>
+        <v>6173296</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4544,19 +4521,24 @@
           <t>Silvåkra</t>
         </is>
       </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>M-Lun-0349</t>
+        </is>
+      </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>1976-04-20</t>
+          <t>1996-09-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1976-04-20</t>
+          <t>1996-09-26</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 5 ex, även hannar med ryggkam.</t>
+          <t>2D5a1528</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4567,80 +4549,79 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>vägkant i odlad granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bertil Johansson</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bertil Johansson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Via Skåne Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3787</t>
+          <t>https://artportalen.se/Sighting/697114</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133324314</v>
+        <v>3787</v>
       </c>
       <c r="B35" t="n">
-        <v>58260</v>
+        <v>58829</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103012</v>
+        <v>100141</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Silvåkragården, Sk</t>
+          <t>Friesendorffs damm, Krankesjön, Sk</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>403444</v>
+        <v>403472</v>
       </c>
       <c r="R35" t="n">
-        <v>6172476</v>
+        <v>6172715</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4667,22 +4648,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>1976-04-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>1976-04-20</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Minst 5 ex, även hannar med ryggkam.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4697,70 +4673,79 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktor Nilsson</t>
+          <t>Bertil Johansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktor Nilsson</t>
+          <t>Bertil Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133324314</t>
+          <t>https://artportalen.se/Sighting/3787</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>93454025</v>
+        <v>133324314</v>
       </c>
       <c r="B36" t="n">
-        <v>43378</v>
+        <v>58260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>201075</v>
+        <v>103012</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Krankesjön, Sk</t>
+          <t>Silvåkragården, Sk</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>403490</v>
+        <v>403444</v>
       </c>
       <c r="R36" t="n">
-        <v>6173258</v>
+        <v>6172476</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4784,22 +4769,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4808,76 +4793,76 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Bergman</t>
+          <t>Viktor Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Bergman</t>
+          <t>Viktor Nilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93454025</t>
+          <t>https://artportalen.se/Sighting/133324314</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3788</v>
+        <v>93454025</v>
       </c>
       <c r="B37" t="n">
-        <v>58826</v>
+        <v>43378</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>208242</v>
+        <v>201075</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Friesendorffs damm, Krankesjön, Sk</t>
+          <t>Krankesjön, Sk</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>403472</v>
+        <v>403490</v>
       </c>
       <c r="R37" t="n">
-        <v>6172715</v>
+        <v>6173258</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4901,12 +4886,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>1976-04-20</t>
+          <t>2015-06-10</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1976-04-20</t>
+          <t>2015-06-10</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4915,33 +4910,34 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bertil Johansson</t>
+          <t>Martin Bergman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bertil Johansson</t>
+          <t>Martin Bergman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3788</t>
+          <t>https://artportalen.se/Sighting/93454025</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3791</v>
+        <v>3788</v>
       </c>
       <c r="B38" t="n">
-        <v>58790</v>
+        <v>58826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4949,16 +4945,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4969,11 +4965,6 @@
       <c r="I38" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5020,11 +5011,6 @@
           <t>1976-04-20</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>några</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5048,16 +5034,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3791</t>
+          <t>https://artportalen.se/Sighting/3788</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3790</v>
+        <v>3791</v>
       </c>
       <c r="B39" t="n">
-        <v>58817</v>
+        <v>58790</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5065,21 +5051,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5164,16 +5150,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3790</t>
+          <t>https://artportalen.se/Sighting/3791</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3789</v>
+        <v>3790</v>
       </c>
       <c r="B40" t="n">
-        <v>58815</v>
+        <v>58817</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5181,26 +5167,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5249,7 +5240,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Cirka</t>
+          <t>några</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5275,7 +5266,251 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/3790</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3789</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Friesendorffs damm, Krankesjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>403472</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6172715</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Silvåkra</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1976-04-20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>1976-04-20</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Cirka</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bertil Johansson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bertil Johansson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/3789</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135719377</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99252</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Silvåkragården, Sk</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>403321</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6172428</v>
+      </c>
+      <c r="S42" t="n">
+        <v>13</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Silvåkra</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ole  Henriksen</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ole  Henriksen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135719377</t>
         </is>
       </c>
     </row>
@@ -5320,6 +5555,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -2944,7 +2944,7 @@
         <v>135494581</v>
       </c>
       <c r="B21" t="n">
-        <v>104419</v>
+        <v>104421</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>135719377</v>
       </c>
       <c r="B42" t="n">
-        <v>99252</v>
+        <v>99254</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -2944,7 +2944,7 @@
         <v>135494581</v>
       </c>
       <c r="B21" t="n">
-        <v>104421</v>
+        <v>104441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>135719377</v>
       </c>
       <c r="B42" t="n">
-        <v>99254</v>
+        <v>99271</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -2944,7 +2944,7 @@
         <v>135494581</v>
       </c>
       <c r="B21" t="n">
-        <v>104441</v>
+        <v>104443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>135719377</v>
       </c>
       <c r="B42" t="n">
-        <v>99271</v>
+        <v>99272</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -5386,7 +5386,7 @@
         <v>135719377</v>
       </c>
       <c r="B42" t="n">
-        <v>99272</v>
+        <v>99273</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -5386,7 +5386,7 @@
         <v>135719377</v>
       </c>
       <c r="B42" t="n">
-        <v>99273</v>
+        <v>99274</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -5386,7 +5386,7 @@
         <v>135719377</v>
       </c>
       <c r="B42" t="n">
-        <v>99274</v>
+        <v>99280</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -5386,7 +5386,7 @@
         <v>135719377</v>
       </c>
       <c r="B42" t="n">
-        <v>99280</v>
+        <v>99281</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -5386,7 +5386,7 @@
         <v>135719377</v>
       </c>
       <c r="B42" t="n">
-        <v>99281</v>
+        <v>99292</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4579,10 +4579,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3787</v>
+        <v>136409054</v>
       </c>
       <c r="B35" t="n">
-        <v>58829</v>
+        <v>96435</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4590,41 +4590,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100141</v>
+        <v>2779</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Friesendorffs damm, Krankesjön, Sk</t>
+          <t>Silvåkragården, Silvåkragården, Sk</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>403472</v>
+        <v>403492</v>
       </c>
       <c r="R35" t="n">
-        <v>6172715</v>
+        <v>6172564</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4648,17 +4644,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>1976-04-20</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>1976-04-20</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Minst 5 ex, även hannar med ryggkam.</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4673,76 +4674,66 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bertil Johansson</t>
+          <t>Jacob Björnberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bertil Johansson</t>
+          <t>Jacob Björnberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3787</t>
+          <t>https://artportalen.se/Sighting/136409054</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133324314</v>
+        <v>3787</v>
       </c>
       <c r="B36" t="n">
-        <v>58260</v>
+        <v>58829</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103012</v>
+        <v>100141</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Silvåkragården, Sk</t>
+          <t>Friesendorffs damm, Krankesjön, Sk</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>403444</v>
+        <v>403472</v>
       </c>
       <c r="R36" t="n">
-        <v>6172476</v>
+        <v>6172715</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4769,22 +4760,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>1976-04-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>1976-04-20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Minst 5 ex, även hannar med ryggkam.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4799,70 +4785,79 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Viktor Nilsson</t>
+          <t>Bertil Johansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktor Nilsson</t>
+          <t>Bertil Johansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133324314</t>
+          <t>https://artportalen.se/Sighting/3787</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>93454025</v>
+        <v>133324314</v>
       </c>
       <c r="B37" t="n">
-        <v>43378</v>
+        <v>58260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>201075</v>
+        <v>103012</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Krankesjön, Sk</t>
+          <t>Silvåkragården, Sk</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>403490</v>
+        <v>403444</v>
       </c>
       <c r="R37" t="n">
-        <v>6173258</v>
+        <v>6172476</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4886,22 +4881,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2015-06-10</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4910,76 +4905,76 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Bergman</t>
+          <t>Viktor Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Bergman</t>
+          <t>Viktor Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93454025</t>
+          <t>https://artportalen.se/Sighting/133324314</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3788</v>
+        <v>93454025</v>
       </c>
       <c r="B38" t="n">
-        <v>58826</v>
+        <v>43378</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208242</v>
+        <v>201075</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Friesendorffs damm, Krankesjön, Sk</t>
+          <t>Krankesjön, Sk</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403472</v>
+        <v>403490</v>
       </c>
       <c r="R38" t="n">
-        <v>6172715</v>
+        <v>6173258</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5003,12 +4998,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>1976-04-20</t>
+          <t>2015-06-10</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1976-04-20</t>
+          <t>2015-06-10</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5017,33 +5022,34 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bertil Johansson</t>
+          <t>Martin Bergman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bertil Johansson</t>
+          <t>Martin Bergman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3788</t>
+          <t>https://artportalen.se/Sighting/93454025</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3791</v>
+        <v>3788</v>
       </c>
       <c r="B39" t="n">
-        <v>58790</v>
+        <v>58826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5051,16 +5057,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5071,11 +5077,6 @@
       <c r="I39" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5122,11 +5123,6 @@
           <t>1976-04-20</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>några</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5150,16 +5146,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3791</t>
+          <t>https://artportalen.se/Sighting/3788</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3790</v>
+        <v>3791</v>
       </c>
       <c r="B40" t="n">
-        <v>58817</v>
+        <v>58790</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5167,21 +5163,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5266,16 +5262,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3790</t>
+          <t>https://artportalen.se/Sighting/3791</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3789</v>
+        <v>3790</v>
       </c>
       <c r="B41" t="n">
-        <v>58815</v>
+        <v>58817</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5283,26 +5279,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5351,7 +5352,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Cirka</t>
+          <t>några</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5377,16 +5378,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3789</t>
+          <t>https://artportalen.se/Sighting/3790</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135719377</v>
+        <v>3789</v>
       </c>
       <c r="B42" t="n">
-        <v>99292</v>
+        <v>58815</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5394,57 +5395,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>208250</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Silvåkragården, Sk</t>
+          <t>Friesendorffs damm, Krankesjön, Sk</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>403321</v>
+        <v>403472</v>
       </c>
       <c r="R42" t="n">
-        <v>6172428</v>
+        <v>6172715</v>
       </c>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5468,22 +5453,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>1976-04-20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>1976-04-20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Cirka</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5492,23 +5472,155 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ole  Henriksen</t>
+          <t>Bertil Johansson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ole  Henriksen</t>
+          <t>Bertil Johansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3789</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135719377</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99292</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Silvåkragården, Sk</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>403321</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6172428</v>
+      </c>
+      <c r="S43" t="n">
+        <v>13</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Silvåkra</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ole  Henriksen</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ole  Henriksen</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135719377</t>
         </is>
@@ -5557,6 +5669,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -4582,7 +4582,7 @@
         <v>136409054</v>
       </c>
       <c r="B35" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -4582,7 +4582,7 @@
         <v>136409054</v>
       </c>
       <c r="B35" t="n">
-        <v>96436</v>
+        <v>96449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -4582,7 +4582,7 @@
         <v>136409054</v>
       </c>
       <c r="B35" t="n">
-        <v>96449</v>
+        <v>96450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
